--- a/localcsms/web/admin-web/src/main/resources/RC_001.xlsx
+++ b/localcsms/web/admin-web/src/main/resources/RC_001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\igKang\workspace\kevit-LocalCsmsWeb_workspace\local-csms\localcsms\web\admin-web\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AntigravityProject\lh\localcsms\web\admin-web\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8914A7C-8DED-46BA-BA19-DC5130EEA436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F5BFE0-9844-4B9D-B549-C16A27276364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4068" yWindow="4188" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,11 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>고객명</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>충전종료시간</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -51,18 +47,10 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>원금액(원)</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>충전ID</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>충전금액(원)</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>충전소명</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -103,10 +91,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>${excelData.chUseCost}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>${excelData.paySum}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -115,10 +99,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>${excelData.companyName}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>${excelData.custName}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -139,15 +119,43 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>소속</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>고객 충전 내역</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>${excelData.mblPhoneNo}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>세대주명</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용금액(원)</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>No.</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>${excelData.seq}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>동</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>호</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>${excelData.dong}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>${excelData.ho}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -161,7 +169,7 @@
     <numFmt numFmtId="178" formatCode="0_);\(0\)"/>
     <numFmt numFmtId="179" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;_р_._-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -175,17 +183,35 @@
       <charset val="204"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
-      <name val="돋움"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="20"/>
-      <name val="돋움"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -267,54 +293,57 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -622,151 +651,157 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:O5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:P5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="26.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="24.5703125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16" style="3" customWidth="1"/>
-    <col min="12" max="14" width="16" style="12" customWidth="1"/>
-    <col min="15" max="15" width="16" style="10" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.109375" style="11"/>
+    <col min="2" max="2" width="28.88671875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" style="11" customWidth="1"/>
+    <col min="4" max="5" width="19.6640625" style="11" customWidth="1"/>
+    <col min="6" max="7" width="16.109375" style="11" customWidth="1"/>
+    <col min="8" max="8" width="26.44140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" style="13" customWidth="1"/>
+    <col min="10" max="10" width="24.5546875" style="13" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" style="13" customWidth="1"/>
+    <col min="12" max="12" width="16" style="14" customWidth="1"/>
+    <col min="13" max="14" width="16" style="15" customWidth="1"/>
+    <col min="15" max="15" width="16" style="16" customWidth="1"/>
+    <col min="16" max="16384" width="9.109375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B1" s="16" t="s">
+    <row r="1" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="B1" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+    </row>
+    <row r="2" spans="2:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+    </row>
+    <row r="3" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:16" ht="19.2" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
+      <c r="G4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-    </row>
-    <row r="3" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:15" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="7" t="s">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="C5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B5" s="4" t="s">
+      <c r="L5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="O5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="5" t="s">
+      <c r="P5" s="10" t="s">
         <v>14</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:O2"/>
+    <mergeCell ref="B1:P1"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/localcsms/web/admin-web/src/main/resources/RC_001.xlsx
+++ b/localcsms/web/admin-web/src/main/resources/RC_001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AntigravityProject\lh\localcsms\web\admin-web\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F5BFE0-9844-4B9D-B549-C16A27276364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D62D6C6-7246-4841-9CF6-56B59A969A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4068" yWindow="4188" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,10 +95,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>고객전화번호</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>${excelData.custName}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -119,18 +115,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>고객 충전 내역</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>${excelData.mblPhoneNo}</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>세대주명</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>사용금액(원)</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -156,6 +140,22 @@
   </si>
   <si>
     <t>${excelData.ho}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>고객 충전 이력</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>${excelData.complexName}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>고객명</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>단지명</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -655,23 +655,23 @@
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="11"/>
-    <col min="2" max="2" width="28.88671875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="29.33203125" style="11" customWidth="1"/>
-    <col min="4" max="5" width="19.6640625" style="11" customWidth="1"/>
-    <col min="6" max="7" width="16.109375" style="11" customWidth="1"/>
-    <col min="8" max="8" width="26.44140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="21.6640625" style="13" customWidth="1"/>
-    <col min="10" max="10" width="24.5546875" style="13" customWidth="1"/>
+    <col min="2" max="3" width="28.88671875" style="11" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" style="11" customWidth="1"/>
+    <col min="5" max="6" width="19.6640625" style="11" customWidth="1"/>
+    <col min="7" max="8" width="16.109375" style="11" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" style="13" customWidth="1"/>
     <col min="11" max="11" width="22.6640625" style="13" customWidth="1"/>
     <col min="12" max="12" width="16" style="14" customWidth="1"/>
     <col min="13" max="14" width="16" style="15" customWidth="1"/>
     <col min="15" max="15" width="16" style="16" customWidth="1"/>
-    <col min="16" max="16384" width="9.109375" style="11"/>
+    <col min="16" max="16" width="21.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.109375" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="17" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
@@ -707,31 +707,31 @@
     <row r="3" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:16" ht="19.2" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>1</v>
@@ -749,42 +749,42 @@
         <v>7</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>16</v>
-      </c>
       <c r="I5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="K5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>11</v>

--- a/localcsms/web/admin-web/src/main/resources/RC_001.xlsx
+++ b/localcsms/web/admin-web/src/main/resources/RC_001.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>충전종료시간</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -115,7 +115,7 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>사용금액(원)</t>
+    <t>청구금액(원)</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
@@ -156,6 +156,22 @@
   </si>
   <si>
     <t>단지명</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>조정금액(원)</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>${excelData.adjustAmount}</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>조정사유</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>${excelData.adjustReason}</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -651,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:P5"/>
+  <dimension ref="B1:R5"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="11"/>
@@ -666,10 +682,12 @@
     <col min="13" max="14" width="16" style="15" customWidth="1"/>
     <col min="15" max="15" width="16" style="16" customWidth="1"/>
     <col min="16" max="16" width="21.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.109375" style="11"/>
+    <col min="17" max="17" width="18" style="11" customWidth="1"/>
+    <col min="18" max="18" width="24" style="11" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="17" t="s">
         <v>27</v>
       </c>
@@ -687,8 +705,10 @@
       <c r="N1" s="17"/>
       <c r="O1" s="17"/>
       <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
     </row>
-    <row r="2" spans="2:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -703,9 +723,11 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
     </row>
-    <row r="3" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:16" ht="19.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:18" ht="19.2" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
@@ -751,8 +773,14 @@
       <c r="P4" s="7" t="s">
         <v>20</v>
       </c>
+      <c r="Q4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>22</v>
       </c>
@@ -797,11 +825,17 @@
       </c>
       <c r="P5" s="10" t="s">
         <v>14</v>
+      </c>
+      <c r="Q5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="B1:R1"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/localcsms/web/admin-web/src/main/resources/RC_001.xlsx
+++ b/localcsms/web/admin-web/src/main/resources/RC_001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AntigravityProject\lh\localcsms\web\admin-web\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D62D6C6-7246-4841-9CF6-56B59A969A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14532E3D-2720-4372-87C4-89BAE0E491EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7776" yWindow="5568" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -179,11 +179,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-* #,##0_р_._-;\-* #,##0_р_._-;_-* &quot;-&quot;_р_._-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="0.00_);\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0_);\(0\)"/>
     <numFmt numFmtId="179" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;_р_._-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -309,7 +310,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -332,15 +333,6 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -361,6 +353,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -670,61 +668,63 @@
   <dimension ref="B1:R5"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="11"/>
-    <col min="2" max="3" width="28.88671875" style="11" customWidth="1"/>
-    <col min="4" max="4" width="29.33203125" style="11" customWidth="1"/>
-    <col min="5" max="6" width="19.6640625" style="11" customWidth="1"/>
-    <col min="7" max="8" width="16.109375" style="11" customWidth="1"/>
-    <col min="9" max="9" width="26.44140625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="21.6640625" style="13" customWidth="1"/>
-    <col min="11" max="11" width="22.6640625" style="13" customWidth="1"/>
-    <col min="12" max="12" width="16" style="14" customWidth="1"/>
-    <col min="13" max="14" width="16" style="15" customWidth="1"/>
-    <col min="15" max="15" width="16" style="16" customWidth="1"/>
-    <col min="16" max="16" width="21.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18" style="11" customWidth="1"/>
-    <col min="18" max="18" width="24" style="11" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="11"/>
+    <col min="1" max="1" width="9.109375" style="8"/>
+    <col min="2" max="2" width="14.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="29.77734375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" style="8" customWidth="1"/>
+    <col min="7" max="8" width="16.109375" style="8" customWidth="1"/>
+    <col min="9" max="9" width="21.77734375" style="8" customWidth="1"/>
+    <col min="10" max="10" width="26" style="10" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="22" style="11" customWidth="1"/>
+    <col min="13" max="14" width="16" style="12" customWidth="1"/>
+    <col min="15" max="15" width="19.77734375" style="13" customWidth="1"/>
+    <col min="16" max="16" width="21.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18" style="8" customWidth="1"/>
+    <col min="18" max="18" width="24" style="8" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="2:18" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
     </row>
     <row r="3" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:18" ht="19.2" x14ac:dyDescent="0.25">
@@ -784,52 +784,52 @@
       <c r="B5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="O5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="P5" s="10" t="s">
+      <c r="P5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="Q5" s="10" t="s">
+      <c r="Q5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="8" t="s">
+      <c r="R5" s="15" t="s">
         <v>34</v>
       </c>
     </row>
